--- a/output/2026-10-02_18_Malesia_Negeri_Sembilan_ATEX_Equipment_Services.xlsx
+++ b/output/2026-10-02_18_Malesia_Negeri_Sembilan_ATEX_Equipment_Services.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato via WebFetch sito ufficiale. Distributore/rappresentante confermato di apparecchiature explosion-proof certificate ATEX/IECEx/IEC/CENELEC/CSA/UL/FM per O&amp;G, petrolchimico, marino.</t>
+          <t>Verificato via WebFetch sito ufficiale. Distributore/rappresentante confermato di apparecchiature explosion-proof certificate ATEX/IECEx/IEC/CENELEC/CSA/UL/FM per O&amp;G, petrolchimico, marino. [DUPLICATO — vedi anche: 2026-10-01_03_Malesia_Kedah_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,6 @@
           <t>See Kwong Electric (KL) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Selangor (Puchong) - copertura nazionale</t>
@@ -573,11 +572,9 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Verificato tramite WebSearch (maukerja.my, sgpgrid.com). Azienda attiva dal 1982, distributore di cable glands, fusibili industriali, prese/spine industriali, illuminazione Ex, certificati ATEX/IECEx/IEC/CSA.</t>
+          <t>Verificato tramite WebSearch (maukerja.my, sgpgrid.com). Azienda attiva dal 1982, distributore di cable glands, fusibili industriali, prese/spine industriali, illuminazione Ex, certificati ATEX/IECEx/IEC/CSA. [DUPLICATO — vedi anche: 2026-10-02_03_Malesia_Melaka_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -592,7 +589,6 @@
           <t>ISEP (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Selangor (Bangi) - copertura nazionale</t>
@@ -603,8 +599,6 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Verificato tramite WebSearch (hiredly.com, malaysiakini.com - vincitore Golden Bull Award 2025). Fornitore di soluzioni/servizi explosion-proof: design, selezione prodotti, installazione, test, commissioning, conformità IECEx/ATEX/NEC 500.</t>
@@ -612,7 +606,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -654,7 +648,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -664,7 +658,6 @@
           <t>EXS Synergy Sdn Bhd</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Selangor (Cyberjaya) / Kuala Lumpur - copertura nazionale/regionale</t>
@@ -675,8 +668,6 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Verificato tramite WebSearch (nodeflair.com, maukerja.my). Primo servizio al mondo certificato IECEx 03-4 per ispezione e manutenzione Ex, gestione EPC per attrezzature Ex, procurement IECEx/ATEX.</t>
@@ -684,7 +675,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -709,8 +700,6 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Verificato via WebFetch pagina ufficiale Deeter Electronics. Rappresentante/distributore di sensori di livello e prodotti per aree pericolose certificati ATEX &amp; IECEx.</t>
@@ -718,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -743,8 +732,6 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Verificato tramite WebSearch (theedgemalaysia.com, iecex.com). Unico Certification Body IECEx del Sud-Est asiatico, offre certificazioni IECEx per equipaggiamenti/atmosfere esplosive.</t>
@@ -752,7 +739,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -782,7 +769,6 @@
           <t>+603-7627 0080</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Verificato tramite WebSearch (sgs.com pagina ufficiale 'explosive atmosphere'; micci.com per sede e telefono Shah Alam). Servizi di certificazione ATEX/IECEx confermati.</t>
@@ -790,7 +776,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -820,7 +806,6 @@
           <t>+603 2160 1088</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Verificato tramite WebSearch: sede DNV Malaysia a Kuala Lumpur (Level 18, Menara Prestige) confermata; servizio di certificazione/compliance ATEX confermato su pagina ufficiale DNV.</t>
@@ -828,7 +813,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -838,7 +823,6 @@
           <t>ExCompliance Sdn Bhd</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Selangor (Shah Alam) - copertura nazionale</t>
@@ -849,8 +833,6 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Verificato tramite WebSearch (jobstore.my). Tra i pionieri del settore Ex in Malesia, top IECEx training provider, consulenza e ispezioni Ex per clienti O&amp;G. Indirizzo: 17A, Jalan Keluli AP7/AP, Taman Perindustrian Bukit Raja Selatan, Shah Alam.</t>
@@ -858,7 +840,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
